--- a/tests/fixtures/System Requirements.xlsx
+++ b/tests/fixtures/System Requirements.xlsx
@@ -1241,7 +1241,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>〇</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>〇</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>〇</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>〇</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1517,7 +1517,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>〇</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1610,7 +1610,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>〇</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>〇</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>〇</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>〇</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1753,7 +1753,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>〇</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
